--- a/order_forms/042_digital_art_print_order_form--order_forms.xlsx
+++ b/order_forms/042_digital_art_print_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'giclée_print'}</t>
+          <t>giclée_print</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'giclée print'}</t>
+          <t>giclée print</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'pigment-based'}</t>
+          <t>pigment-based</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'pigment-based'}</t>
+          <t>pigment-based</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'landscape'}</t>
+          <t>landscape</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'landscape'}</t>
+          <t>landscape</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'portrait'}</t>
+          <t>portrait</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'portrait'}</t>
+          <t>portrait</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'paper_type_1'}</t>
+          <t>paper_type_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'paper_type_1'}</t>
+          <t>paper type 1</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'paper_type_2'}</t>
+          <t>paper_type_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'paper_type_2'}</t>
+          <t>paper type 2</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'paper_type_3'}</t>
+          <t>paper_type_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'paper_type_3'}</t>
+          <t>paper type 3</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_41,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 41, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_42,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 42, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_43,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 43, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_44,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 44, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': 'bank_transfer'}</t>
+          <t>bank transfer</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_51,_'name':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 51, 'name': 'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
     </row>
